--- a/important_mails_2026-07-26.xlsx
+++ b/important_mails_2026-07-26.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,126 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sun, 26 Jul 2026 14:21:34 +0000</t>
+          <t>Sun, 26 Jul 2026 20:49:44 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>Your FBA request is complete (1pqaY5uvK2)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-5941114-2816300
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-2040695819658286</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026 14:44:02 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $63.02 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202607261349
+ Was this email helpful?
+ SPC-USAmazon-175924099412243</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026 14:21:34 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -531,39 +636,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:21:01 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -583,39 +688,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:20:18 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -635,39 +740,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:57:25 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -683,39 +788,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 05:07:54 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -731,39 +836,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 16:10:45 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -779,39 +884,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 10:35:17 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Zx1U3/hDuM)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -831,39 +936,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 05:01:14 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -879,39 +984,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 05:03:32 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -927,39 +1032,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -975,39 +1080,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1023,40 +1128,40 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:09:39 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Verstrek KYC-verificatie binnen 45 dagen om beperkingen te
  voorkomen</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Verstrek KYC-verificatie binnen 45 dagen om beperkingen te voorkomen
@@ -1075,39 +1180,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:52:41 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -1126,39 +1231,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:42:14 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -1177,39 +1282,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:24:08 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Fournissez une vérification KYC sous 45 jours pour éviter les restrictions</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Fournissez une vérification KYC sous 45 jours pour éviter les restrictions
@@ -1225,39 +1330,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -1274,39 +1379,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -1344,39 +1449,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:31:05 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -1393,125 +1498,6 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
-[需要采取的操作] 需要您的“我要开店”付款账户的相关信息
- [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
- 您好！
-此次联系您是因为我们需要一些其他文件才能继续验证您的账户。
-提供经过修改或篡改的文件可能会导致账户被永久关闭。
-我们仅允许修改银行对账单等文件，以遮挡付款余额等详细信息。
-如果我未采取措施或者不提供所需的信息/文件，会怎么样？
-自我们首次与您联系要求您采取措施或提供完成验证所需的所有文件和信息之日起，您总共有 60 天的时间来提供这些文件和信息。我们审核和验证您采取措施后的结果的时间或验证信息的时间不会计入给您的 60 天期限。
-如果您未能在 60 天内采取措施或提供要求的信息，您的商品将被暂时停售，并且您的提现功能将被暂时停用，直到完成验证为止。
-如果自我们首次联系您之日起已超过 60 天，则您的付款可能已被冻结，您的商品可能已被停售。在您提供要求的信息或文件且您的账户得到验证之前，您的付款将继续处于冻结状态，您的商品将继续处于停售状态。
-为什么会发生这种情况？
-您之前提供的银行账户所有权证明文件不足以完成验证流程，因为它它并未体现您账户上注册的**完整**公司名称。
-我需要提供哪种类型的文件？
--- 目前在卖家平台中输入为存款方式的其中2个银行账户的银行对账单或银行资信证明的扫描件：以 *29 和 *91 结尾的账号。
-如何处理这种情况？
-确保文件符合以下标准：
--- 文件必须是在最近 180 天内开具的。
--- 文件必须显示银行账号、银行徽标和账户持有者姓名。
--- 如果您以公司形式开展业务，则您的银行账户必须为公司账户。
--- 请务必确保文件清晰易读。
--- 文件不能是屏幕截图。
--- 文件必须使用我们支持的语言之一。我们支持以下语言：英语、中文、丹麦语、荷兰语、德语、意大利语、西班牙语、瑞典语、法语、土耳其语、波兰语、葡萄牙语、阿拉伯语、印地语、泰米尔语、越南语、泰语、韩语和日语。如果原始文件使用的不是我们支持的语言，请同时提供原始文件和翻译文件。
-我如何提供这些信息？
-请完成以下步骤，在卖家平台的“银行账户信息”部分更新您的银行账户信息：
-https://sellercentral-europe.amazon.com/sw/AccountInfo/DepositMethodView/step/DepositMethodView
-1.单击“更换存款方式”。
-2.在新出现的页面上，单击“添加新的存款方式”，并提供您尝试注册的银行账户的详细信息。
-3.单击“设置存款方式”。
-4.单击“验证账户”。
-5.转至卖家平台的“身份信息”部分：
-https://sellercentral-europe.amazon.com/sw/SSR/BusinessKYCInfo/spaDashboard
-6.按照相关提示上传要求提供的文</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Know Your Customer (KYC) verification process support</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
- Pending Know Your Customer (KYC) account verification
- Hello,
- We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
- Submit documentation
- In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
- What happens next?
- Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
- Once the verification is complete, you will receive a performance notification and email advising you of the result.
- We’re here to help.
- If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
- For more informa</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1516,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sun, 19 Jul 2026 15:59:18 +0000</t>
+          <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4959,7 +4945,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4974,40 +4960,41 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
+          <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
+ Pending Know Your Customer (KYC) account verification
+ Hello,
+ We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
+ Submit documentation
+ In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
+ What happens next?
+ Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
+ Once the verification is complete, you will receive a performance notification and email advising you of the result.
+ We’re here to help.
+ If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
+ For more informa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5022,42 +5009,55 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
+          <t>Sun, 19 Jul 2026 15:59:18 +0000</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (HI24ImSBWG)</t>
+          <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-4837972-8437069
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1301823993910502</t>
+          <t>96
+[需要采取的操作] 需要您的“我要开店”付款账户的相关信息
+ [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
+ 您好！
+此次联系您是因为我们需要一些其他文件才能继续验证您的账户。
+提供经过修改或篡改的文件可能会导致账户被永久关闭。
+我们仅允许修改银行对账单等文件，以遮挡付款余额等详细信息。
+如果我未采取措施或者不提供所需的信息/文件，会怎么样？
+自我们首次与您联系要求您采取措施或提供完成验证所需的所有文件和信息之日起，您总共有 60 天的时间来提供这些文件和信息。我们审核和验证您采取措施后的结果的时间或验证信息的时间不会计入给您的 60 天期限。
+如果您未能在 60 天内采取措施或提供要求的信息，您的商品将被暂时停售，并且您的提现功能将被暂时停用，直到完成验证为止。
+如果自我们首次联系您之日起已超过 60 天，则您的付款可能已被冻结，您的商品可能已被停售。在您提供要求的信息或文件且您的账户得到验证之前，您的付款将继续处于冻结状态，您的商品将继续处于停售状态。
+为什么会发生这种情况？
+您之前提供的银行账户所有权证明文件不足以完成验证流程，因为它它并未体现您账户上注册的**完整**公司名称。
+我需要提供哪种类型的文件？
+-- 目前在卖家平台中输入为存款方式的其中2个银行账户的银行对账单或银行资信证明的扫描件：以 *29 和 *91 结尾的账号。
+如何处理这种情况？
+确保文件符合以下标准：
+-- 文件必须是在最近 180 天内开具的。
+-- 文件必须显示银行账号、银行徽标和账户持有者姓名。
+-- 如果您以公司形式开展业务，则您的银行账户必须为公司账户。
+-- 请务必确保文件清晰易读。
+-- 文件不能是屏幕截图。
+-- 文件必须使用我们支持的语言之一。我们支持以下语言：英语、中文、丹麦语、荷兰语、德语、意大利语、西班牙语、瑞典语、法语、土耳其语、波兰语、葡萄牙语、阿拉伯语、印地语、泰米尔语、越南语、泰语、韩语和日语。如果原始文件使用的不是我们支持的语言，请同时提供原始文件和翻译文件。
+我如何提供这些信息？
+请完成以下步骤，在卖家平台的“银行账户信息”部分更新您的银行账户信息：
+https://sellercentral-europe.amazon.com/sw/AccountInfo/DepositMethodView/step/DepositMethodView
+1.单击“更换存款方式”。
+2.在新出现的页面上，单击“添加新的存款方式”，并提供您尝试注册的银行账户的详细信息。
+3.单击“设置存款方式”。
+4.单击“验证账户”。
+5.转至卖家平台的“身份信息”部分：
+https://sellercentral-europe.amazon.com/sw/SSR/BusinessKYCInfo/spaDashboard
+6.按照相关提示上传要求提供的文</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
+          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7355,112 +7355,11 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 06/26/26 14:37 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 262,76.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 06/26/26 14:37 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 621.84.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7479,40 +7378,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
  Inventory Portal</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
@@ -7520,39 +7419,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 17:38:33 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -7572,39 +7471,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 16:17:59 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -7624,39 +7523,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:36 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7675,40 +7574,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:22:39 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Get answers from the people who build the tools you use every day.
  Save $100</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49s9x/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4bmtj/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
@@ -7725,39 +7624,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:08:44 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7776,40 +7675,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 08:00:54 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7824,40 +7723,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 05:35:29 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7882,40 +7781,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7930,39 +7829,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -7980,40 +7879,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -8030,40 +7929,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -8075,39 +7974,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 13:53:00 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8122,39 +8021,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Global Warehousing and Distribution’s new China shipping options are live</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Choose Shanghai or Shenzhen with Free on Board support
@@ -8169,39 +8068,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo]
 We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
@@ -8219,40 +8118,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -8266,39 +8165,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -8314,40 +8213,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 22:17:55 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for
  6/2026</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for 6/2026
  96
@@ -8369,39 +8268,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:24:05 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -8423,39 +8322,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:47 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8470,40 +8369,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 23:30:27 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -8521,39 +8420,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 20:04:53 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -8572,39 +8471,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 15:47:06 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -8622,39 +8521,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 14:10:23 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -8672,39 +8571,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:46:14 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -8723,39 +8622,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 10:28:11 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -8774,39 +8673,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 09:08:55 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -8825,39 +8724,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 08:53:55 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -8895,40 +8794,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -8946,39 +8845,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -8997,39 +8896,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -9047,39 +8946,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -9098,39 +8997,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -9149,39 +9048,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -9200,39 +9099,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:12 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 6/2026
  96
@@ -9250,39 +9149,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:22:50 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 6/2026
  96
@@ -9306,39 +9205,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 04:18:37 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 6/2026
  96
@@ -9365,39 +9264,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:58:57 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9424,39 +9323,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:24:51 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -9479,39 +9378,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:10:44 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 6/2026
  96
@@ -9535,39 +9434,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 03:00:23 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 6/2026
  96
@@ -9594,39 +9493,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:41:16 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -9653,39 +9552,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:20:20 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 6/2026
  96
@@ -9705,39 +9604,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:05:26 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 6/2026
  96
@@ -9760,39 +9659,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 02:01:10 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9817,39 +9716,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:33:27 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -9868,39 +9767,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:22:23 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 6/2026
  96
@@ -9918,39 +9817,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 00:13:46 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -9975,39 +9874,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 23:07:09 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10026,39 +9925,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:44:31 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -10083,39 +9982,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:29:53 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 6/2026
  96
@@ -10140,39 +10039,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:23:16 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10191,39 +10090,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 21:07:51 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -10250,39 +10149,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:56:46 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -10309,39 +10208,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:36:00 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -10366,39 +10265,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:27:56 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 6/2026
  96
@@ -10425,39 +10324,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:23:50 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10481,39 +10380,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 6/2026
  96
@@ -10540,39 +10439,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 20:02:23 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -10599,39 +10498,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:58:54 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -10658,39 +10557,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:55:57 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 6/2026
  96
@@ -10715,39 +10614,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:16:22 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -10774,39 +10673,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 19:05:55 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 6/2026
  96
@@ -10831,39 +10730,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:55:02 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -10881,39 +10780,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 18:14:51 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -10937,39 +10836,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:47:27 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 6/2026
  96
@@ -10996,39 +10895,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:46:42 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 6/2026
  96
@@ -11046,39 +10945,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:31:36 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -11103,39 +11002,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:28:53 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -11153,39 +11052,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:10:41 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -11209,39 +11108,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 17:01:49 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -11259,39 +11158,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:42:42 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 6/2026
  96
@@ -11309,39 +11208,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:21:50 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 6/2026
  96
@@ -11368,39 +11267,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 16:02:53 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 6/2026
  96
@@ -11425,40 +11324,40 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:46:03 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk
  sales</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.co.uk sales
  96
@@ -11473,39 +11372,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:40:18 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 6/2026
  96
@@ -11526,39 +11425,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 6/2026
  96
@@ -11582,39 +11481,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 15:30:53 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -11632,39 +11531,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 14:51:08 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 6/2026
  96
@@ -11687,39 +11586,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:53:08 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11734,39 +11633,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 12:49:39 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11781,39 +11680,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -11827,39 +11726,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -11877,39 +11776,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -11924,39 +11823,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -11973,39 +11872,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -12023,39 +11922,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -12070,39 +11969,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12118,207 +12017,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 06/26/26 14:40 CEST, nous avons effectué un virement d’un montant de €
- 207.53 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de p</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de
-análisis ha señalado que una asociación con usted sería una gran oportunidad
-para ambos.
-¿Estaría
-disponible para una reunión online esta semana?
-Acerca de Worten
-- Somos el líder del mercado portugués:
-- Nº 1 del
-comercio electrónico portugués
-- Sitio web con
-mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200
-tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de
-gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes los 6 meses iniciales
-Estaré encantado
-de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos
-Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>Tus límites de capacidad de Logística de Amazon para julio</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>96
- Tus límites de capacidad de Logística de Amazon para julio
- Hola:
- Se confirmaron tus límites de capacidad para el próximo periodo.
- Pronóstico de capacidad para el periodo del jul. 1 al 31, a partir del jun. 24:
- Tipo de almacenamiento
- Límite de capacidad total (metros cúbicos)
- Tamaño estándar
- 16.42
- Tamaño grande
- 21.66
- Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
- En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del jun. 23.
- Tipo de almacenamiento
- Uso sin los envíos abiertos incluidos (metros cúbicos)
- Uso con los envíos abiertos incluidos (metros cúbicos)
- Tamaño estándar
- 0.00
- 0.00
- Tamaño grande
- 0.00
- 0.00
- Cómo se establecen los límites de capacidad de Logística de Amazon
- Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 04:29:33 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-30</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12341,39 +12072,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 04:12:27 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12398,39 +12129,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 03:41:39 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12453,39 +12184,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12506,39 +12237,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12561,39 +12292,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12616,39 +12347,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12672,39 +12403,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12727,39 +12458,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12780,39 +12511,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12836,39 +12567,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12892,39 +12623,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12946,39 +12677,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
@@ -12990,39 +12721,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Your Accelerate 2026 session catalog is now live</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
@@ -13034,40 +12765,40 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -13084,39 +12815,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
